--- a/src/test/resources/ImportTemplate/Checksum - Redshift.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum - Redshift.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333946DA-C9CD-4FB4-B7A6-E131BC5BB3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251342CA-958A-46E6-9AD2-C4AB9B6510B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <t>SELECT Count(*) AS TARGET_Count from icedqrs.regression_database.reg_employee</t>
   </si>
   <si>
-    <t>Checksum_ImportSQL--Redshift--regEmployee_table</t>
+    <t>Checksum_ImportSQL--CDW-Redshift_RegEmployee</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Checksum - Redshift.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum - Redshift.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251342CA-958A-46E6-9AD2-C4AB9B6510B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E3AD18-0DBD-46DC-9753-ED550DCB0FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
     <t>SELECT Count(*) AS TARGET_Count from icedqrs.regression_database.reg_employee</t>
   </si>
   <si>
-    <t>Checksum_ImportSQL--CDW-Redshift_RegEmployee</t>
+    <t>Checksum_ImportSQL__CDW_Redshift_RegEmployee</t>
   </si>
 </sst>
 </file>
